--- a/artfynd/A 54706-2021 artfynd.xlsx
+++ b/artfynd/A 54706-2021 artfynd.xlsx
@@ -1048,7 +1048,7 @@
         <v>113335788</v>
       </c>
       <c r="B5" t="n">
-        <v>55987</v>
+        <v>55988</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 54706-2021 artfynd.xlsx
+++ b/artfynd/A 54706-2021 artfynd.xlsx
@@ -1048,11 +1048,11 @@
         <v>113335788</v>
       </c>
       <c r="B5" t="n">
-        <v>55988</v>
+        <v>55991</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">

--- a/artfynd/A 54706-2021 artfynd.xlsx
+++ b/artfynd/A 54706-2021 artfynd.xlsx
@@ -1048,7 +1048,7 @@
         <v>113335788</v>
       </c>
       <c r="B5" t="n">
-        <v>55991</v>
+        <v>55995</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 54706-2021 artfynd.xlsx
+++ b/artfynd/A 54706-2021 artfynd.xlsx
@@ -1048,7 +1048,7 @@
         <v>113335788</v>
       </c>
       <c r="B5" t="n">
-        <v>55995</v>
+        <v>56002</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 54706-2021 artfynd.xlsx
+++ b/artfynd/A 54706-2021 artfynd.xlsx
@@ -1048,7 +1048,7 @@
         <v>113335788</v>
       </c>
       <c r="B5" t="n">
-        <v>56002</v>
+        <v>56004</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 54706-2021 artfynd.xlsx
+++ b/artfynd/A 54706-2021 artfynd.xlsx
@@ -1048,7 +1048,7 @@
         <v>113335788</v>
       </c>
       <c r="B5" t="n">
-        <v>56004</v>
+        <v>56032</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 54706-2021 artfynd.xlsx
+++ b/artfynd/A 54706-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 54706-2021 artfynd.xlsx
+++ b/artfynd/A 54706-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>23613539</v>
+        <v>47805086</v>
       </c>
       <c r="B2" t="n">
-        <v>56811</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57966</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,31 +686,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102999</v>
+        <v>100048</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>427017.7028163208</v>
+        <v>427018</v>
       </c>
       <c r="R2" t="n">
-        <v>6498392.229332758</v>
+        <v>6498392</v>
       </c>
       <c r="S2" t="n">
         <v>33</v>
@@ -754,22 +749,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2006-06-18</t>
+          <t>2013-12-09</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2006-06-18</t>
+          <t>2013-12-09</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,44 +779,43 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mattias Winther</t>
+          <t>Patrick Åström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mattias Winther</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Patrick Åström</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Skådarhjälpen</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>47805086</v>
+        <v>113335788</v>
       </c>
       <c r="B3" t="n">
-        <v>56401</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57144</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100048</v>
+        <v>102613</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -834,21 +828,28 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>födosökande</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kalvaklippekärret, Lugnåsberget, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>427017.7028163208</v>
+        <v>427018</v>
       </c>
       <c r="R3" t="n">
-        <v>6498392.229332758</v>
+        <v>6498392</v>
       </c>
       <c r="S3" t="n">
         <v>33</v>
@@ -875,22 +876,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2013-12-09</t>
+          <t>2023-11-19</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2013-12-09</t>
+          <t>2023-11-19</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>I toppen på björk</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,31 +911,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Patrick Åström</t>
+          <t>Mona-Lisa Axelsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Patrick Åström</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Skådarhjälpen</t>
-        </is>
-      </c>
+          <t>Mona-Lisa Axelsson, Christina Sandblom, Ingemar Johansson, Saga Boberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>95920852</v>
       </c>
       <c r="B4" t="n">
-        <v>55803</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57317</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -973,10 +970,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>427017.7028163208</v>
+        <v>427018</v>
       </c>
       <c r="R4" t="n">
-        <v>6498392.229332758</v>
+        <v>6498392</v>
       </c>
       <c r="S4" t="n">
         <v>33</v>
@@ -1045,56 +1042,47 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113335788</v>
+        <v>95920892</v>
       </c>
       <c r="B5" t="n">
-        <v>56481</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58209</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102613</v>
+        <v>102980</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Ladusvala</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Hirundo rustica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kalvaklippekärret, Lugnåsberget, Vg</t>
@@ -1131,27 +1119,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-11-19</t>
+          <t>2021-09-05</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-11-19</t>
+          <t>2021-09-05</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>I toppen på björk</t>
+          <t>Ca</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1166,15 +1154,131 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Mona-Lisa Axelsson</t>
+          <t>Staffan Mogren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Mona-Lisa Axelsson, Christina Sandblom, Ingemar Johansson, Saga Boberg</t>
+          <t>Staffan Mogren, Lars Grimborg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>23613539</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58393</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>102999</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Björktrast</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Turdus pilaris</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kalvaklippekärret, Lugnåsberget, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>427018</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6498392</v>
+      </c>
+      <c r="S6" t="n">
+        <v>33</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Mariestad</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Lugnås</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2006-06-18</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2006-06-18</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mattias Winther</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Mattias Winther</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 54706-2021 artfynd.xlsx
+++ b/artfynd/A 54706-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -792,6 +797,11 @@
           <t>Skådarhjälpen</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/47805086</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -920,6 +930,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113335788</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1039,6 +1054,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95920852</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1163,6 +1183,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95920892</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1279,8 +1304,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/23613539</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>